--- a/onagawa_water_tariff/02_deliverables/01_rate_reform_simulation_MAIN.xlsx
+++ b/onagawa_water_tariff/02_deliverables/01_rate_reform_simulation_MAIN.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.00&quot;倍&quot;"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -167,6 +167,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -266,7 +272,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -314,11 +320,46 @@
       <top style="medium"/>
       <bottom style="medium"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -821,6 +862,17 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1186,7 +1238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1207,6 +1259,15 @@
           <t>女川町水道事業　料金改定検討　前提条件（入力セル）</t>
         </is>
       </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="6" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -1215,13 +1276,35 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="5" customHeight="1"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="174" t="inlineStr">
+        <is>
+          <t>【この版は中間報告書（改訂版）の前提と一致しません】　計算根拠には使用しないでください。　本文の数値は 09_interim_report/onagawa_adopted_calc.xlsx（採用計算表）で再現します。</t>
+        </is>
+      </c>
+      <c r="B3" s="175" t="n"/>
+      <c r="C3" s="175" t="n"/>
+      <c r="D3" s="175" t="n"/>
+      <c r="E3" s="175" t="n"/>
+      <c r="F3" s="175" t="n"/>
+      <c r="G3" s="175" t="n"/>
+      <c r="H3" s="175" t="n"/>
+    </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>【A】料金算定対象期間</t>
         </is>
       </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="6" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1272,6 +1355,12 @@
           <t>水道法施行規則第12条「おおむね3年」 → 実務標準5年</t>
         </is>
       </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -1294,6 +1383,12 @@
           <t>対象資産の基準日</t>
         </is>
       </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="6" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -1312,6 +1407,12 @@
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -1334,6 +1435,12 @@
           <t>仕様書「9月末中間報告」に対応。最終報告後に議決が前提</t>
         </is>
       </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="6" t="n"/>
     </row>
     <row r="10" ht="5" customHeight="1"/>
     <row r="11" ht="16" customHeight="1">
@@ -1342,6 +1449,15 @@
           <t>【B】資産維持費率　★ここを変更すると全シートが再計算されます</t>
         </is>
       </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="6" t="n"/>
     </row>
     <row r="12" ht="12" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1431,6 +1547,7 @@
           <t>日本水道協会「水道料金算定要領」標準3%。業務仕様書では3%を正式ケースとして指定。</t>
         </is>
       </c>
+      <c r="J14" s="6" t="n"/>
     </row>
     <row r="15" ht="5" customHeight="1"/>
     <row r="16" ht="16" customHeight="1">
@@ -1439,6 +1556,15 @@
           <t>【C】対象資産（資産維持費の算定基礎）</t>
         </is>
       </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="6" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -1487,6 +1613,12 @@
           <t>試算シート【料金算定】資産維持費シート帳簿価額。R8固定資産台帳で要更新。</t>
         </is>
       </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="6" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
@@ -1507,6 +1639,12 @@
           <t>推計値。R8〜R12の減価償却・新規取得を考慮。確定後に要修正。</t>
         </is>
       </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="6" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
@@ -1528,6 +1666,12 @@
           <t>自動計算 =(B18+B19)/2</t>
         </is>
       </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="6" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
@@ -1549,6 +1693,12 @@
           <t>自動計算 =B20×B14（資産維持率）</t>
         </is>
       </c>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="6" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
@@ -1570,6 +1720,12 @@
           <t>自動計算 =B21×5</t>
         </is>
       </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="6" t="n"/>
     </row>
     <row r="23" ht="5" customHeight="1"/>
     <row r="24" ht="16" customHeight="1">
@@ -1578,6 +1734,15 @@
           <t>【D】有収水量・料金収入（R8〜R12推計）</t>
         </is>
       </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="6" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
@@ -1638,6 +1803,10 @@
           <t>管路更新10.4億円集中年度</t>
         </is>
       </c>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="6" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -1662,6 +1831,10 @@
           <t>北上川導水管工事着手</t>
         </is>
       </c>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="6" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
@@ -1682,6 +1855,10 @@
         <v>118312</v>
       </c>
       <c r="F28" s="21" t="inlineStr"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="6" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
@@ -1702,6 +1879,10 @@
         <v>116955</v>
       </c>
       <c r="F29" s="21" t="inlineStr"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="6" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="29" t="inlineStr">
@@ -1722,6 +1903,10 @@
         <v>114135</v>
       </c>
       <c r="F30" s="21" t="inlineStr"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="6" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="33" t="inlineStr">
@@ -1729,19 +1914,19 @@
           <t>5年合計</t>
         </is>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="118">
         <f>SUM(B26:B30)</f>
         <v/>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="118">
         <f>SUM(C26:C30)</f>
         <v/>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="118">
         <f>ROUND(AVERAGE(D26:D30),0)</f>
         <v/>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="118">
         <f>SUM(E26:E30)</f>
         <v/>
       </c>
@@ -1750,6 +1935,10 @@
           <t>5年合計・平均</t>
         </is>
       </c>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -1813,6 +2002,17 @@
           <t>女川町水道事業　総括原価の算定　R8〜R12（5年間）　資産維持費3%を正式ケースとして算入</t>
         </is>
       </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+      <c r="K1" s="5" t="n"/>
+      <c r="L1" s="6" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -1821,12 +2021,36 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="5" customHeight="1"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="174" t="inlineStr">
+        <is>
+          <t>【この版は中間報告書（改訂版）の前提と一致しません】　計算根拠には使用しないでください。　本文の数値は 09_interim_report/onagawa_adopted_calc.xlsx（採用計算表）で再現します。</t>
+        </is>
+      </c>
+      <c r="B3" s="175" t="n"/>
+      <c r="C3" s="175" t="n"/>
+      <c r="D3" s="175" t="n"/>
+      <c r="E3" s="175" t="n"/>
+      <c r="F3" s="175" t="n"/>
+      <c r="G3" s="175" t="n"/>
+      <c r="H3" s="175" t="n"/>
+    </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="36">
         <f>" ▶ 現在の資産維持率："&amp;TEXT('01_前提条件'!B14,"0.00%")&amp;"　資産維持費（年間）："&amp;TEXT('01_前提条件'!B21,"#,##0")&amp;"千円"&amp;"　総括原価5年："&amp;TEXT(H23*1000,"#,##0")&amp;"百万円"</f>
         <v/>
       </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="6" t="n"/>
     </row>
     <row r="5" ht="5" customHeight="1"/>
     <row r="6" ht="16" customHeight="1">
@@ -1835,6 +2059,17 @@
           <t>【費目別原価集計】　単位：千円</t>
         </is>
       </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="6" t="n"/>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1924,7 +2159,7 @@
       <c r="G8" s="38" t="n">
         <v>137024</v>
       </c>
-      <c r="H8" s="34">
+      <c r="H8" s="118">
         <f>SUM(C8:G8)</f>
         <v/>
       </c>
@@ -1932,7 +2167,7 @@
         <f>H8/5</f>
         <v/>
       </c>
-      <c r="J8" s="40">
+      <c r="J8" s="149">
         <f>IF(H15&lt;&gt;0,ABS(H8)/ABS(H15),0)</f>
         <v/>
       </c>
@@ -1973,7 +2208,7 @@
       <c r="G9" s="38" t="n">
         <v>402234</v>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="118">
         <f>SUM(C9:G9)</f>
         <v/>
       </c>
@@ -1981,7 +2216,7 @@
         <f>H9/5</f>
         <v/>
       </c>
-      <c r="J9" s="40">
+      <c r="J9" s="149">
         <f>IF(H15&lt;&gt;0,ABS(H9)/ABS(H15),0)</f>
         <v/>
       </c>
@@ -2022,7 +2257,7 @@
       <c r="G10" s="42" t="n">
         <v>9288</v>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="118">
         <f>SUM(C10:G10)</f>
         <v/>
       </c>
@@ -2030,7 +2265,7 @@
         <f>H10/5</f>
         <v/>
       </c>
-      <c r="J10" s="40">
+      <c r="J10" s="149">
         <f>IF(H15&lt;&gt;0,ABS(H10)/ABS(H15),0)</f>
         <v/>
       </c>
@@ -2071,7 +2306,7 @@
       <c r="G11" s="42" t="n">
         <v>38700</v>
       </c>
-      <c r="H11" s="34">
+      <c r="H11" s="118">
         <f>SUM(C11:G11)</f>
         <v/>
       </c>
@@ -2079,7 +2314,7 @@
         <f>H11/5</f>
         <v/>
       </c>
-      <c r="J11" s="40">
+      <c r="J11" s="149">
         <f>IF(H15&lt;&gt;0,ABS(H11)/ABS(H15),0)</f>
         <v/>
       </c>
@@ -2105,27 +2340,27 @@
           <t>＋</t>
         </is>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="83">
         <f>'01_前提条件'!B21</f>
         <v/>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="83">
         <f>'01_前提条件'!B21</f>
         <v/>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="83">
         <f>'01_前提条件'!B21</f>
         <v/>
       </c>
-      <c r="F12" s="44">
+      <c r="F12" s="83">
         <f>'01_前提条件'!B21</f>
         <v/>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="83">
         <f>'01_前提条件'!B21</f>
         <v/>
       </c>
-      <c r="H12" s="44">
+      <c r="H12" s="83">
         <f>SUM(C12:G12)</f>
         <v/>
       </c>
@@ -2133,7 +2368,7 @@
         <f>H12/5</f>
         <v/>
       </c>
-      <c r="J12" s="46">
+      <c r="J12" s="86">
         <f>IF(H15&lt;&gt;0,ABS(H12)/ABS(H15),0)</f>
         <v/>
       </c>
@@ -2174,7 +2409,7 @@
       <c r="G13" s="50" t="n">
         <v>-86000</v>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="118">
         <f>SUM(C13:G13)</f>
         <v/>
       </c>
@@ -2223,7 +2458,7 @@
       <c r="G14" s="50" t="n">
         <v>-3000</v>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="118">
         <f>SUM(C14:G14)</f>
         <v/>
       </c>
@@ -2295,6 +2530,17 @@
           <t>【給水原価・料金回収率の算定】（前提シート連動で自動計算）</t>
         </is>
       </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="6" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="61" t="inlineStr">
@@ -2341,6 +2587,8 @@
           <t>4,316,000㎥</t>
         </is>
       </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="6" t="n"/>
       <c r="E19" s="63" t="n"/>
       <c r="F19" s="64" t="n"/>
       <c r="G19" s="21" t="inlineStr">
@@ -2348,6 +2596,11 @@
           <t>財政シミュ水需要予測より</t>
         </is>
       </c>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="6" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
@@ -2359,6 +2612,8 @@
         <f>H15&amp;"千円"</f>
         <v/>
       </c>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="6" t="n"/>
       <c r="E20" s="63" t="n"/>
       <c r="F20" s="66" t="n"/>
       <c r="G20" s="21" t="inlineStr">
@@ -2366,6 +2621,11 @@
           <t>上記費目合計（資産維持率連動）</t>
         </is>
       </c>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="6" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="43" t="inlineStr">
@@ -2377,6 +2637,8 @@
         <f>ROUND(H15*1000/4316000,1)&amp;"円/㎥"</f>
         <v/>
       </c>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="6" t="n"/>
       <c r="E21" s="21" t="inlineStr">
         <is>
           <t>約242円（R5実績逆算）</t>
@@ -2388,6 +2650,11 @@
           <t>総括原価×1000÷有収水量。R5実績の料金回収率52.87%から逆算した242円とは別概念（注参照）</t>
         </is>
       </c>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="6" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
@@ -2400,6 +2667,8 @@
           <t>128.2円/㎥</t>
         </is>
       </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="6" t="n"/>
       <c r="E22" s="63" t="n"/>
       <c r="F22" s="66" t="n"/>
       <c r="G22" s="21" t="inlineStr">
@@ -2407,6 +2676,11 @@
           <t>131,429千円÷1,025千㎥（R7実績）</t>
         </is>
       </c>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="6" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="43" t="inlineStr">
@@ -2418,6 +2692,8 @@
         <f>TEXT(128.2/ROUND(H15*1000/4316000,1),"0.0%")&amp;"（総括原価ベース）"</f>
         <v/>
       </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="6" t="n"/>
       <c r="E23" s="21" t="inlineStr">
         <is>
           <t>52.87%（R5実績ベース）</t>
@@ -2429,6 +2705,11 @@
           <t>【重要】R5実績242円ベースと総括原価572円ベースの乖離に注意（md Section5.2参照）</t>
         </is>
       </c>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="6" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
@@ -2441,6 +2722,8 @@
           <t>約192円/㎥</t>
         </is>
       </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="6" t="n"/>
       <c r="E24" s="63" t="n"/>
       <c r="F24" s="66" t="n"/>
       <c r="G24" s="21" t="inlineStr">
@@ -2448,6 +2731,11 @@
           <t>基本料金1.5倍・超過+22円の改定案。R5実績ベースの料金回収率は79%に改善。</t>
         </is>
       </c>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="6" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="43" t="inlineStr">
@@ -2460,6 +2748,8 @@
           <t>約79%</t>
         </is>
       </c>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="6" t="n"/>
       <c r="E25" s="21" t="inlineStr">
         <is>
           <t>100%（目標）</t>
@@ -2471,6 +2761,11 @@
           <t>R5実績給水原価242円ベース。総括原価ベースでは約34%。段階改定の必要性を示す。</t>
         </is>
       </c>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="6" t="n"/>
     </row>
     <row r="26" ht="50" customHeight="1">
       <c r="A26" s="69" t="inlineStr">
@@ -2480,9 +2775,36 @@
 ② R8〜R12総括原価ベース（給水原価約572円）：改定後でも回収率約34%。段階改定・繰入金の必要性を説明する場面で使用。</t>
         </is>
       </c>
-    </row>
-    <row r="27"/>
-    <row r="28"/>
+      <c r="B26" s="176" t="n"/>
+      <c r="C26" s="176" t="n"/>
+      <c r="D26" s="176" t="n"/>
+      <c r="E26" s="176" t="n"/>
+      <c r="F26" s="176" t="n"/>
+      <c r="G26" s="176" t="n"/>
+      <c r="H26" s="176" t="n"/>
+      <c r="I26" s="176" t="n"/>
+      <c r="J26" s="176" t="n"/>
+      <c r="K26" s="176" t="n"/>
+      <c r="L26" s="177" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="178" t="n"/>
+      <c r="L27" s="179" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="180" t="n"/>
+      <c r="B28" s="181" t="n"/>
+      <c r="C28" s="181" t="n"/>
+      <c r="D28" s="181" t="n"/>
+      <c r="E28" s="181" t="n"/>
+      <c r="F28" s="181" t="n"/>
+      <c r="G28" s="181" t="n"/>
+      <c r="H28" s="181" t="n"/>
+      <c r="I28" s="181" t="n"/>
+      <c r="J28" s="181" t="n"/>
+      <c r="K28" s="181" t="n"/>
+      <c r="L28" s="182" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="29">
     <mergeCell ref="L9"/>
@@ -2549,6 +2871,18 @@
           <t>女川町水道事業　料金改定シミュレーション①　現行体系維持案（仕様書パターン1）</t>
         </is>
       </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+      <c r="K1" s="5" t="n"/>
+      <c r="L1" s="5" t="n"/>
+      <c r="M1" s="6" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -2564,6 +2898,18 @@
           <t>【A】資産維持率別 必要改定率・供給単価（前提シートB14と連動）</t>
         </is>
       </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -2821,6 +3167,18 @@
           <t>【B】水量ゾーン別 改定案の影響試算（現行体系維持・一律引き上げ）</t>
         </is>
       </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="6" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="61" t="inlineStr">
@@ -3253,6 +3611,18 @@
           <t>【年間換算増収額と目標不足額との比較】</t>
         </is>
       </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="6" t="n"/>
     </row>
     <row r="25" ht="12" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -3459,6 +3829,17 @@
           <t>女川町水道事業　料金改定シミュレーション②　赤字半減案（仕様書パターン2）</t>
         </is>
       </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+      <c r="K1" s="5" t="n"/>
+      <c r="L1" s="6" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -3474,6 +3855,17 @@
           <t>【A】「赤字」の定義と現状値（3パターンで明確化）</t>
         </is>
       </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="6" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
@@ -3519,11 +3911,18 @@
           <t>営業収益−営業費用　R7推計　約▲383,000千円/年</t>
         </is>
       </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="21" t="inlineStr">
         <is>
           <t>純粋な事業収支。最も厳しい数字。住民への説明で「水道は赤字」と言える根拠。</t>
         </is>
       </c>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="6" t="n"/>
       <c r="K6" s="124" t="inlineStr">
         <is>
           <t>使用</t>
@@ -3542,11 +3941,18 @@
           <t>収益的収入−収益的支出　R7推計　約▲19,415千円/年</t>
         </is>
       </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="21" t="inlineStr">
         <is>
           <t>損益計算書ベースの経常損益。決算上の評価に使用。</t>
         </is>
       </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="6" t="n"/>
       <c r="K7" s="10" t="inlineStr">
         <is>
           <t>参考</t>
@@ -3567,11 +3973,18 @@
 約▲74,302千円/年（3%）</t>
         </is>
       </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="21" t="inlineStr">
         <is>
           <t>料金で賄えていない実態額。料金改定で埋めるべき金額の最小限。最も政策的に有用な指標。</t>
         </is>
       </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="6" t="n"/>
       <c r="K8" s="127" t="inlineStr">
         <is>
           <t>★主用</t>
@@ -3590,11 +4003,18 @@
           <t>総括原価−現行料金収入　R8〜R12推計（3%）　約▲392,271千円/年</t>
         </is>
       </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="6" t="n"/>
       <c r="E9" s="21" t="inlineStr">
         <is>
           <t>減価償却費（非キャッシュ）含む。全額料金回収は現実的でない。将来財源確保の目標値。</t>
         </is>
       </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="6" t="n"/>
       <c r="K9" s="10" t="inlineStr">
         <is>
           <t>参考</t>
@@ -3608,6 +4028,17 @@
           <t>【B】赤字半減目標の設定と必要改定率（定義③：キャッシュ不足額ベース）</t>
         </is>
       </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="6" t="n"/>
     </row>
     <row r="12" ht="12" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -3700,6 +4131,9 @@
         <v>1.787114134849716</v>
       </c>
       <c r="I14" s="21" t="inlineStr"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="6" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="43" t="inlineStr">
@@ -3733,6 +4167,9 @@
           <t>仕様書パターン2：赤字半減</t>
         </is>
       </c>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="6" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="70" t="inlineStr">
@@ -3762,6 +4199,9 @@
         <v>0.5957147934401814</v>
       </c>
       <c r="I16" s="21" t="inlineStr"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="6" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -3795,6 +4235,9 @@
           <t>段階改定の最終到達点</t>
         </is>
       </c>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="6" t="n"/>
     </row>
     <row r="18" ht="5" customHeight="1"/>
     <row r="19" ht="16" customHeight="1">
@@ -3803,6 +4246,17 @@
           <t>【C】段階改定スケジュール案（赤字半減→完全解消 2段階）</t>
         </is>
       </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="6" t="n"/>
     </row>
     <row r="20" ht="12" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -3994,6 +4448,19 @@
           <t>女川町水道事業　料金改定シミュレーション③　口径別料金表案（仕様書パターン3）</t>
         </is>
       </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+      <c r="K1" s="5" t="n"/>
+      <c r="L1" s="5" t="n"/>
+      <c r="M1" s="5" t="n"/>
+      <c r="N1" s="6" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -4009,6 +4476,19 @@
           <t>【パターン3-A】口径別基本料金＋段階逓増従量料金（標準型）</t>
         </is>
       </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="6" t="n"/>
     </row>
     <row r="5" ht="12" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -4377,6 +4857,19 @@
           <t>【パターン3-B】口径別体系＋産業用特例区分（塩竈モデル参考・水産加工業配慮）</t>
         </is>
       </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="6" t="n"/>
     </row>
     <row r="16" ht="12" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -4489,6 +4982,11 @@
           <t>現行逓減制からの移行がスムーズ。塩竈市が既に運用実績あり（参考事例）。収入減少リスクは現行比軽微。</t>
         </is>
       </c>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="6" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="125" t="inlineStr">
@@ -4539,6 +5037,11 @@
           <t>段階改定と組み合わせることで急激な負担増を回避。経過措置期間を10年とすることで事業者の設備投資計画に影響を与えない。</t>
         </is>
       </c>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="6" t="n"/>
     </row>
     <row r="20" ht="5" customHeight="1"/>
     <row r="21" ht="55" customHeight="1">
@@ -4549,9 +5052,40 @@
 ※「塩竈モデルを全県全水産加工業者に適用すべき」という表現は避けること。全県適用時は収入減・補填財源・対象限定の制度設計が必要。</t>
         </is>
       </c>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
+      <c r="B21" s="176" t="n"/>
+      <c r="C21" s="176" t="n"/>
+      <c r="D21" s="176" t="n"/>
+      <c r="E21" s="176" t="n"/>
+      <c r="F21" s="176" t="n"/>
+      <c r="G21" s="176" t="n"/>
+      <c r="H21" s="176" t="n"/>
+      <c r="I21" s="176" t="n"/>
+      <c r="J21" s="176" t="n"/>
+      <c r="K21" s="176" t="n"/>
+      <c r="L21" s="176" t="n"/>
+      <c r="M21" s="176" t="n"/>
+      <c r="N21" s="177" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="178" t="n"/>
+      <c r="N22" s="179" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="180" t="n"/>
+      <c r="B23" s="181" t="n"/>
+      <c r="C23" s="181" t="n"/>
+      <c r="D23" s="181" t="n"/>
+      <c r="E23" s="181" t="n"/>
+      <c r="F23" s="181" t="n"/>
+      <c r="G23" s="181" t="n"/>
+      <c r="H23" s="181" t="n"/>
+      <c r="I23" s="181" t="n"/>
+      <c r="J23" s="181" t="n"/>
+      <c r="K23" s="181" t="n"/>
+      <c r="L23" s="181" t="n"/>
+      <c r="M23" s="181" t="n"/>
+      <c r="N23" s="182" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A21:N23"/>
@@ -4600,6 +5134,19 @@
           <t>女川町水道事業　水産加工業（19社モデル）への料金改定影響試算</t>
         </is>
       </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+      <c r="K1" s="5" t="n"/>
+      <c r="L1" s="5" t="n"/>
+      <c r="M1" s="5" t="n"/>
+      <c r="N1" s="6" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -4615,6 +5162,19 @@
           <t>【水産加工業19社モデル】月間使用水量・現行料金・改定案別比較</t>
         </is>
       </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="6" t="n"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -4991,6 +5551,17 @@
           <t>女川町水道事業　料金改定案 A〜E案 横断比較表（仕様書対応・住民議会説明用）</t>
         </is>
       </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+      <c r="K1" s="5" t="n"/>
+      <c r="L1" s="6" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -5006,6 +5577,17 @@
           <t>【改定案 A〜E案の概要比較】</t>
         </is>
       </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="158" t="inlineStr">
@@ -5078,6 +5660,7 @@
           <t>現行の用途別・逓減制を維持したまま総括原価不足分を改定</t>
         </is>
       </c>
+      <c r="C6" s="6" t="n"/>
       <c r="D6" s="160" t="n">
         <v>28159</v>
       </c>
@@ -5111,6 +5694,8 @@
           <t>第1候補。現行制度維持で説明容易。仕様書パターン1</t>
         </is>
       </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="6" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="161" t="inlineStr">
@@ -5124,6 +5709,7 @@
           <t>現行体系維持・赤字半減を目標とした段階的改定</t>
         </is>
       </c>
+      <c r="C7" s="6" t="n"/>
       <c r="D7" s="162" t="n">
         <v>196136</v>
       </c>
@@ -5157,6 +5743,8 @@
           <t>段階改定の現実案。仕様書パターン2。中間報告で提示に最適</t>
         </is>
       </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="6" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="163" t="inlineStr">
@@ -5171,6 +5759,7 @@
           <t>口径別基本料金＋段階逓増従量料金へ移行（標準型）</t>
         </is>
       </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="164" t="n">
         <v>5386479</v>
       </c>
@@ -5204,6 +5793,8 @@
           <t>単独採用は慎重。水産加工業影響試算が必須。仕様書パターン3-A</t>
         </is>
       </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="6" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="165" t="inlineStr">
@@ -5218,6 +5809,7 @@
           <t>口径別体系＋水産加工業向け産業用特例区分（塩竈モデル）</t>
         </is>
       </c>
+      <c r="C9" s="6" t="n"/>
       <c r="D9" s="144" t="inlineStr">
         <is>
           <t>─（産業特例による収入減を考慮）</t>
@@ -5253,6 +5845,8 @@
           <t>塩竈モデルを参考にした産業配慮案。C案の補完。仕様書パターン3-B</t>
         </is>
       </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="6" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="166" t="inlineStr">
@@ -5267,6 +5861,7 @@
           <t>5〜10年で段階的に改定（B案の長期版・複数案の組み合わせ）</t>
         </is>
       </c>
+      <c r="C10" s="6" t="n"/>
       <c r="D10" s="168" t="inlineStr">
         <is>
           <t>─（段階ごとに設定）</t>
@@ -5302,6 +5897,8 @@
           <t>激変緩和として最も受容されやすい。B案との組み合わせで実効性向上</t>
         </is>
       </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="6" t="n"/>
     </row>
     <row r="11" ht="5" customHeight="1"/>
     <row r="12" ht="12" customHeight="1">
@@ -5322,8 +5919,8 @@
   <mergeCells count="15">
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="J6:L6"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="J6:L6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="J10:L10"/>
     <mergeCell ref="A1:L1"/>
@@ -5367,6 +5964,15 @@
           <t>女川町水道事業　料金改定の必要性と改定案の概要　【住民・議会説明用】</t>
         </is>
       </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="6" t="n"/>
     </row>
     <row r="2" ht="8" customHeight="1"/>
     <row r="3" ht="16" customHeight="1">
@@ -5375,6 +5981,15 @@
           <t>① なぜ料金改定が必要か</t>
         </is>
       </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="6" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
@@ -5425,6 +6040,12 @@
           <t>R5実績：給水原価242円/㎥に対し供給単価128円/㎥。約半分しか回収できていない。「水1㎥あたり約114円を補助等で補填している」と説明。</t>
         </is>
       </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="6" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="172" t="inlineStr">
@@ -5447,6 +6068,12 @@
           <t>収益的支出が収益的収入を超過。現行料金を維持し続けると財政悪化が加速する。</t>
         </is>
       </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="6" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="170" t="inlineStr">
@@ -5470,6 +6097,12 @@
           <t>老朽施設の大規模更新が集中する。料金収入で財源の一部を賄う必要がある。</t>
         </is>
       </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="6" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="172" t="inlineStr">
@@ -5492,6 +6125,12 @@
           <t>PDF資料2-2（厚生労働省）：資産維持費3%を総括原価に算入し、将来の更新財源を料金で確保することが求められている。</t>
         </is>
       </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="6" t="n"/>
     </row>
     <row r="9" ht="5" customHeight="1"/>
     <row r="10" ht="16" customHeight="1">
@@ -5500,6 +6139,15 @@
           <t>② 改定案の比較（3案・シンプル版）</t>
         </is>
       </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="6" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="4" t="inlineStr"/>
@@ -5540,16 +6188,21 @@
           <t>用途別・逓減制維持のまま単価引き上げ</t>
         </is>
       </c>
+      <c r="C12" s="6" t="n"/>
       <c r="D12" s="7" t="inlineStr">
         <is>
           <t>段階的に赤字半減を目指す</t>
         </is>
       </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="6" t="n"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
           <t>口径別移行＋水産加工業特例</t>
         </is>
       </c>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="6" t="n"/>
       <c r="J12" s="173" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
@@ -5563,16 +6216,21 @@
           <t>990→1,320〜1,540円</t>
         </is>
       </c>
+      <c r="C13" s="6" t="n"/>
       <c r="D13" s="9" t="inlineStr">
         <is>
           <t>990→1,200〜1,300円（段階）</t>
         </is>
       </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="6" t="n"/>
       <c r="G13" s="9" t="inlineStr">
         <is>
           <t>口径別：13mm1,100〜20mm1,320円</t>
         </is>
       </c>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="6" t="n"/>
       <c r="J13" s="66" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
@@ -5586,16 +6244,21 @@
           <t>121→132〜143円/㎥</t>
         </is>
       </c>
+      <c r="C14" s="6" t="n"/>
       <c r="D14" s="7" t="inlineStr">
         <is>
           <t>121→132円/㎥</t>
         </is>
       </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="6" t="n"/>
       <c r="G14" s="7" t="inlineStr">
         <is>
           <t>121→132〜143円（段階逓増）</t>
         </is>
       </c>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="6" t="n"/>
       <c r="J14" s="173" t="n"/>
     </row>
     <row r="15" ht="26" customHeight="1">
@@ -5611,18 +6274,23 @@
 （+625〜850円）</t>
         </is>
       </c>
+      <c r="C15" s="6" t="n"/>
       <c r="D15" s="9" t="inlineStr">
         <is>
           <t>現行2,395円→2,715〜2,895円
 （+320〜500円）</t>
         </is>
       </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="6" t="n"/>
       <c r="G15" s="9" t="inlineStr">
         <is>
           <t>現行2,395円→2,860〜3,020円
 （+465〜625円）</t>
         </is>
       </c>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="6" t="n"/>
       <c r="J15" s="66" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
@@ -5638,18 +6306,23 @@
 （+21.9%）</t>
         </is>
       </c>
+      <c r="C16" s="6" t="n"/>
       <c r="D16" s="7" t="inlineStr">
         <is>
           <t>現行111,980円→125,000〜130,000円
 （+11〜16%）</t>
         </is>
       </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="6" t="n"/>
       <c r="G16" s="7" t="inlineStr">
         <is>
           <t>産業特例適用で115,500円
 （+3.1%、ほぼ現行維持）</t>
         </is>
       </c>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="6" t="n"/>
       <c r="J16" s="173" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
@@ -5663,16 +6336,21 @@
           <t>約35,000千円</t>
         </is>
       </c>
+      <c r="C17" s="6" t="n"/>
       <c r="D17" s="9" t="inlineStr">
         <is>
           <t>約37,000千円</t>
         </is>
       </c>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="6" t="n"/>
       <c r="G17" s="9" t="inlineStr">
         <is>
           <t>産業特例収入減あり（別途試算）</t>
         </is>
       </c>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="6" t="n"/>
       <c r="J17" s="66" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
@@ -5686,16 +6364,21 @@
           <t>パターン1</t>
         </is>
       </c>
+      <c r="C18" s="6" t="n"/>
       <c r="D18" s="7" t="inlineStr">
         <is>
           <t>パターン2</t>
         </is>
       </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="6" t="n"/>
       <c r="G18" s="7" t="inlineStr">
         <is>
           <t>パターン3-B</t>
         </is>
       </c>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="6" t="n"/>
       <c r="J18" s="173" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
@@ -5709,16 +6392,21 @@
           <t>◎ 第1候補</t>
         </is>
       </c>
+      <c r="C19" s="6" t="n"/>
       <c r="D19" s="9" t="inlineStr">
         <is>
           <t>◎ 段階改定として推奨</t>
         </is>
       </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="6" t="n"/>
       <c r="G19" s="9" t="inlineStr">
         <is>
           <t>○ C案の補完として提示</t>
         </is>
       </c>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="6" t="n"/>
       <c r="J19" s="66" t="n"/>
     </row>
     <row r="20" ht="5" customHeight="1"/>
